--- a/docs/hoses/Huls 19001.xlsx
+++ b/docs/hoses/Huls 19001.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://groupiph-my.sharepoint.com/personal/patrick_debrabander_geeve_com/Documents/Downloads/Selector/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="965" documentId="8_{EF3304FA-BEB0-41A8-B5C3-5BC144BE2E73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6CEACE3A-8173-478B-9709-DD9C48EB892D}"/>
+  <xr:revisionPtr revIDLastSave="1240" documentId="8_{EF3304FA-BEB0-41A8-B5C3-5BC144BE2E73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CAEBCB1F-D7A6-4720-B644-469425DF1F8C}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{F99E09F2-8A0D-45FD-B5D4-06449184F1A9}"/>
+    <workbookView xWindow="34005" yWindow="3105" windowWidth="21600" windowHeight="11385" xr2:uid="{F99E09F2-8A0D-45FD-B5D4-06449184F1A9}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -24,11 +24,11 @@
     <definedName name="ExactAddinReport1.Data.3" localSheetId="0" hidden="1">"ms.Warehouse, Items.UserNumber_05, ItemAccounts.PurchasePrice, ItemAccounts.ItemCodeAccount, cicmpy.crdnr, Items.ID, Items.IsSerialNumberItem, ItemAssortment.Description_0 AS [ItemAssortment.Description] FROM Items\n LEFT JOIN ItemAssortment ON Items."</definedName>
     <definedName name="ExactAddinReport1.Data.4" localSheetId="0" hidden="1">"Assortment = ItemAssortment.Assortment AND Items.Assortment IS NOT NULL AND ItemAssortment.Assortment IS NOT NULL \n LEFT JOIN ItemAccounts ON Items.Itemcode=ItemAccounts.ItemCode AND Items.lev_crdnr=ItemAccounts.crdnr  AND Items.Itemcode IS NOT NULL "</definedName>
     <definedName name="ExactAddinReport1.Data.5" localSheetId="0" hidden="1">"AND ItemAccounts.ItemCode IS NOT NULL AND Items.lev_crdnr IS NOT NULL AND ItemAccounts.crdnr IS NOT NULL \n LEFT JOIN cicmpy ON cicmpy.crdnr = ItemAccounts.crdnr  AND cicmpy.crdnr IS NOT NULL AND ItemAccounts.crdnr IS NOT NULL \n WHERE ((Items.Conditi"</definedName>
-    <definedName name="ExactAddinReport1.Data.6" localSheetId="0" hidden="1">"on IN ('A','B','D','F','E') AND (Items.Type IN ('S','B') ) AND Items.ItemCode IN (SELECT artcode FROM voorrd JOIN pwmagaz ON voorrd.magcode = pwmagaz.magcode AND pwmagaz.res_id = 119 ))) AND Items.ItemCode LIKE '%9223-%' ORDER BY Items.ItemCode;Header"</definedName>
-    <definedName name="ExactAddinReport1.Data.7" localSheetId="0" hidden="1">"=-1;System.Company=005;System.New=0;System.Wizard=Select;System.Update=-1"</definedName>
+    <definedName name="ExactAddinReport1.Data.6" localSheetId="0" hidden="1">"on IN ('A','B','D','F','E') AND (Items.Type IN ('S','B') ) AND Items.ItemCode IN (SELECT artcode FROM voorrd JOIN pwmagaz ON voorrd.magcode = pwmagaz.magcode AND pwmagaz.res_id = 119 ))) AND Items.ItemCode LIKE '%19001-%' ORDER BY Items.ItemCode;Heade"</definedName>
+    <definedName name="ExactAddinReport1.Data.7" localSheetId="0" hidden="1">"r=-1;System.Company=005;System.New=0;System.Wizard=Select;System.Update=-1"</definedName>
     <definedName name="ExactAddinReports" hidden="1">1</definedName>
     <definedName name="Report1.Header">Blad1!$A$1:$Q$1</definedName>
-    <definedName name="Report1.Range">Blad1!$A$2:$Q$24</definedName>
+    <definedName name="Report1.Range">Blad1!$A$2:$Q$15</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -54,150 +54,189 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
-  <si>
-    <t>Artikelnummer</t>
-  </si>
-  <si>
-    <t>Omschrijving</t>
-  </si>
-  <si>
-    <t>9223-014</t>
-  </si>
-  <si>
-    <t>MARKING FERRULE 1/4"-14 MM I.D. SS-316-L</t>
-  </si>
-  <si>
-    <t>9223-017</t>
-  </si>
-  <si>
-    <t>MARKING FERRULE 3/8"-17 MM I.D. SS-316-L</t>
-  </si>
-  <si>
-    <t>9223-019</t>
-  </si>
-  <si>
-    <t>MARKING FERRULE 3/8"- 19 MM I.D. SS-316-L</t>
-  </si>
-  <si>
-    <t>9223-020</t>
-  </si>
-  <si>
-    <t>MARKING FERRULE 1/2"-19 MM I.D. SS-316-L</t>
-  </si>
-  <si>
-    <t>9223-022</t>
-  </si>
-  <si>
-    <t>MARKING FERRULE 1/2"-22 MM I.D. SS-316-L</t>
-  </si>
-  <si>
-    <t>9223-023</t>
-  </si>
-  <si>
-    <t>MARKING FERRULE 5/8"-25 MM I.D. SS-316L-L</t>
-  </si>
-  <si>
-    <t>9223-027</t>
-  </si>
-  <si>
-    <t>MARKING FERRULE 5/8"-25 MM I.D. SS-316-L</t>
-  </si>
-  <si>
-    <t>9223-030</t>
-  </si>
-  <si>
-    <t>MARKING FERRULE 3/4"-30 MM I.D. SS-316-L</t>
-  </si>
-  <si>
-    <t>9223-032</t>
-  </si>
-  <si>
-    <t>MARKING FERRULE 3/4"-32 MM I.D. SS-316-L</t>
-  </si>
-  <si>
-    <t>9223-035</t>
-  </si>
-  <si>
-    <t>MARKING FERRULE 1"-35 MM I.D. SS-316-L</t>
-  </si>
-  <si>
-    <t>9223-037</t>
-  </si>
-  <si>
-    <t>MARKING FERRULE 1"-37 MM I.D. SS-316-L</t>
-  </si>
-  <si>
-    <t>9223-040</t>
-  </si>
-  <si>
-    <t>MARKING FERRULE 40 MM I.D. SS-303/304-L</t>
-  </si>
-  <si>
-    <t>9223-044</t>
-  </si>
-  <si>
-    <t>MARKING FERRULE 44.3 MM I.D. SS-316-L</t>
-  </si>
-  <si>
-    <t>9223-045</t>
-  </si>
-  <si>
-    <t>MARKING FERRULE 45 MM I.D. SS-303/304-L</t>
-  </si>
-  <si>
-    <t>9223-047</t>
-  </si>
-  <si>
-    <t>MARKING FERRULE 47.8 MM I.D. SS-316-L</t>
-  </si>
-  <si>
-    <t>9223-053</t>
-  </si>
-  <si>
-    <t>MARKING FERRULE 53 MM I.D. SS-303/304-L</t>
-  </si>
-  <si>
-    <t>9223-056</t>
-  </si>
-  <si>
-    <t>MARKING FERRULE 56 MM I.D. SS-316-L</t>
-  </si>
-  <si>
-    <t>9223-066</t>
-  </si>
-  <si>
-    <t>MARKING FERRULE 66 MM I.D. SS-303/304-L</t>
-  </si>
-  <si>
-    <t>9223-072</t>
-  </si>
-  <si>
-    <t>MARKING FERRULE 72 MM I.D. SS-303/304-L</t>
-  </si>
-  <si>
-    <t>9223-080</t>
-  </si>
-  <si>
-    <t>MARKING FERRULE 80 MM I.D. SS-303/304-l</t>
-  </si>
-  <si>
-    <t>9223-094</t>
-  </si>
-  <si>
-    <t>MARKING FERRULE 94 MM I.D. SS-303/304-L</t>
-  </si>
-  <si>
-    <t>9223-102</t>
-  </si>
-  <si>
-    <t>MARKING FERRULE 102 MM I.D. SS-303/304-L</t>
-  </si>
-  <si>
-    <t>9223-127</t>
-  </si>
-  <si>
-    <t>MARKING FERRULE 127 MM I.D. SS-303/304-L</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="61">
+  <si>
+    <t>Items.ItemCode</t>
+  </si>
+  <si>
+    <t>[Items.Description]</t>
+  </si>
+  <si>
+    <t>Items.Condition</t>
+  </si>
+  <si>
+    <t>Items.IsSalesItem</t>
+  </si>
+  <si>
+    <t>Items.IsPurchaseItem</t>
+  </si>
+  <si>
+    <t>Items.IsAssembled</t>
+  </si>
+  <si>
+    <t>Items.IsStockItem</t>
+  </si>
+  <si>
+    <t>HasPicture</t>
+  </si>
+  <si>
+    <t>SalesPackagePrice</t>
+  </si>
+  <si>
+    <t>Items.Warehouse</t>
+  </si>
+  <si>
+    <t>Items.UserNumber_05</t>
+  </si>
+  <si>
+    <t>ItemAccounts.PurchasePrice</t>
+  </si>
+  <si>
+    <t>ItemAccounts.ItemCodeAccount</t>
+  </si>
+  <si>
+    <t>cicmpy.crdnr</t>
+  </si>
+  <si>
+    <t>Items.ID</t>
+  </si>
+  <si>
+    <t>Items.IsSerialNumberItem</t>
+  </si>
+  <si>
+    <t>[ItemAssortment.Description]</t>
+  </si>
+  <si>
+    <t>19001-24</t>
+  </si>
+  <si>
+    <t>HULS TEXSLEEVE STEEL 24X1.5X20</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>SFR-2124</t>
+  </si>
+  <si>
+    <t>SLANG BESCHERMING</t>
+  </si>
+  <si>
+    <t>19001-25</t>
+  </si>
+  <si>
+    <t>HULS TEXSLEEVE STEEL 25X1.5X20</t>
+  </si>
+  <si>
+    <t>SFR-2225</t>
+  </si>
+  <si>
+    <t>19001-27</t>
+  </si>
+  <si>
+    <t>HULS TEXSLEEVE STEEL 27X1.5X20</t>
+  </si>
+  <si>
+    <t>SFR-2427</t>
+  </si>
+  <si>
+    <t>19001-30</t>
+  </si>
+  <si>
+    <t>HULS TEXSLEEVE STEEL 30X1.5X20</t>
+  </si>
+  <si>
+    <t>SFR-2730</t>
+  </si>
+  <si>
+    <t>19001-32</t>
+  </si>
+  <si>
+    <t>HULS TEXSLEEVE STEEL 32X1.5X20</t>
+  </si>
+  <si>
+    <t>SFR-2932</t>
+  </si>
+  <si>
+    <t>19001-35</t>
+  </si>
+  <si>
+    <t>HULS TEXSLEEVE STEEL 35X1.5X20</t>
+  </si>
+  <si>
+    <t>SFR-3235</t>
+  </si>
+  <si>
+    <t>19001-38</t>
+  </si>
+  <si>
+    <t>HULS TEXSLEEVE STEEL 38X1.5X20</t>
+  </si>
+  <si>
+    <t>SFR-3538</t>
+  </si>
+  <si>
+    <t>19001-40</t>
+  </si>
+  <si>
+    <t>HULS TEXSLEEVE STEEL 40X1.5X20</t>
+  </si>
+  <si>
+    <t>SFR-3740</t>
+  </si>
+  <si>
+    <t>19001-45</t>
+  </si>
+  <si>
+    <t>HULS TEXSLEEVE STEEL 45X1.5X30</t>
+  </si>
+  <si>
+    <t>SFR-4245</t>
+  </si>
+  <si>
+    <t>19001-52</t>
+  </si>
+  <si>
+    <t>HULS TEXSLEEVE STEEL 52X2.0X30</t>
+  </si>
+  <si>
+    <t>SFR4852</t>
+  </si>
+  <si>
+    <t>19001-55</t>
+  </si>
+  <si>
+    <t>HULS TEXSLEEVE STEEL 55X2.0X30</t>
+  </si>
+  <si>
+    <t>SFR-5155</t>
+  </si>
+  <si>
+    <t>19001-70</t>
+  </si>
+  <si>
+    <t>HULS TEXSLEEVE STEEL 70X2.5X30</t>
+  </si>
+  <si>
+    <t>SFR6570</t>
+  </si>
+  <si>
+    <t>19001-75</t>
+  </si>
+  <si>
+    <t>HULS TEXSLEEVE STEEL 75X2.5X30</t>
+  </si>
+  <si>
+    <t>SFR7075</t>
+  </si>
+  <si>
+    <t>19001-85</t>
+  </si>
+  <si>
+    <t>HULS TEXSLEEVE STEEL 85X2.5X30</t>
+  </si>
+  <si>
+    <t>SFR8085</t>
   </si>
 </sst>
 </file>
@@ -569,203 +608,806 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3475DC1B-1FB6-4B75-B6F9-5A00C335501C}">
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>4.09</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>456</v>
+      </c>
+      <c r="L2">
+        <v>0.78110000000000002</v>
+      </c>
+      <c r="M2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N2">
+        <v>100546</v>
+      </c>
+      <c r="O2">
+        <v>43038</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>3.59</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>13</v>
+      </c>
+      <c r="L3">
+        <v>0.67</v>
+      </c>
+      <c r="M3" t="s">
+        <v>24</v>
+      </c>
+      <c r="N3">
+        <v>100546</v>
+      </c>
+      <c r="O3">
+        <v>95431</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>26</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>4.2699999999999996</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>114</v>
+      </c>
+      <c r="L4">
+        <v>0.85319999999999996</v>
+      </c>
+      <c r="M4" t="s">
+        <v>27</v>
+      </c>
+      <c r="N4">
+        <v>100546</v>
+      </c>
+      <c r="O4">
+        <v>35078</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>29</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>5.25</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>67</v>
+      </c>
+      <c r="L5">
+        <v>1.0396000000000001</v>
+      </c>
+      <c r="M5" t="s">
+        <v>30</v>
+      </c>
+      <c r="N5">
+        <v>100546</v>
+      </c>
+      <c r="O5">
+        <v>95432</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>6.02</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>68</v>
+      </c>
+      <c r="L6">
+        <v>1.1138999999999999</v>
+      </c>
+      <c r="M6" t="s">
+        <v>33</v>
+      </c>
+      <c r="N6">
+        <v>100546</v>
+      </c>
+      <c r="O6">
+        <v>43035</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>6.58</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>19</v>
+      </c>
+      <c r="L7">
+        <v>1.2617</v>
+      </c>
+      <c r="M7" t="s">
+        <v>36</v>
+      </c>
+      <c r="N7">
+        <v>100546</v>
+      </c>
+      <c r="O7">
+        <v>119048</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>6.92</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>19</v>
+      </c>
+      <c r="L8">
+        <v>1.4234</v>
+      </c>
+      <c r="M8" t="s">
+        <v>39</v>
+      </c>
+      <c r="N8">
+        <v>100546</v>
+      </c>
+      <c r="O8">
+        <v>43036</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>7.8</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>41</v>
+      </c>
+      <c r="L9">
+        <v>1.502</v>
+      </c>
+      <c r="M9" t="s">
+        <v>42</v>
+      </c>
+      <c r="N9">
+        <v>100546</v>
+      </c>
+      <c r="O9">
+        <v>119044</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>8.39</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>17</v>
+      </c>
+      <c r="L10">
+        <v>1.7784</v>
+      </c>
+      <c r="M10" t="s">
+        <v>45</v>
+      </c>
+      <c r="N10">
+        <v>100546</v>
+      </c>
+      <c r="O10">
+        <v>119043</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>14.09</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>13</v>
+      </c>
+      <c r="L11">
+        <v>2.71</v>
+      </c>
+      <c r="M11" t="s">
+        <v>48</v>
+      </c>
+      <c r="N11">
+        <v>100546</v>
+      </c>
+      <c r="O11">
+        <v>43037</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>14.85</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <v>52</v>
+      </c>
+      <c r="L12">
+        <v>2.8</v>
+      </c>
+      <c r="M12" t="s">
+        <v>51</v>
+      </c>
+      <c r="N12">
+        <v>100546</v>
+      </c>
+      <c r="O12">
+        <v>95437</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>28.18</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="K13">
+        <v>13</v>
+      </c>
+      <c r="L13">
+        <v>5.9611999999999998</v>
+      </c>
+      <c r="M13" t="s">
+        <v>54</v>
+      </c>
+      <c r="N13">
+        <v>100546</v>
+      </c>
+      <c r="O13">
+        <v>119045</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>28.76</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14">
+        <v>20</v>
+      </c>
+      <c r="L14">
+        <v>5.53</v>
+      </c>
+      <c r="M14" t="s">
+        <v>57</v>
+      </c>
+      <c r="N14">
+        <v>100546</v>
+      </c>
+      <c r="O14">
+        <v>119046</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>41.39</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15">
         <v>11</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="L15">
+        <v>7.95</v>
+      </c>
+      <c r="M15" t="s">
+        <v>60</v>
+      </c>
+      <c r="N15">
+        <v>100546</v>
+      </c>
+      <c r="O15">
+        <v>119047</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>36</v>
-      </c>
-      <c r="B19" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>44</v>
-      </c>
-      <c r="B23" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>46</v>
-      </c>
-      <c r="B24" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
